--- a/templates/template-shopee.xlsx
+++ b/templates/template-shopee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t>et_title_product_id</t>
   </si>
@@ -144,7 +144,1615 @@
     <t>49379453</t>
   </si>
   <si>
-    <t>{"search_condition":{}}</t>
+    <t>{"search_condition":{"pre_order_condition":2}}</t>
+  </si>
+  <si>
+    <t>56111749702</t>
+  </si>
+  <si>
+    <t>Mug Keramik 110ml - Cangkir Kopi Gelas Teh Mug Ocha | Neko Tanapijak</t>
+  </si>
+  <si>
+    <t>272674959529</t>
+  </si>
+  <si>
+    <t>Biru</t>
+  </si>
+  <si>
+    <t>mug-neko-110ml</t>
+  </si>
+  <si>
+    <t>mug-neko-110ml-biru</t>
+  </si>
+  <si>
+    <t>26500</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>272674959528</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>mug-neko-110ml-orange</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>55161749728</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kanu Tanapijak</t>
+  </si>
+  <si>
+    <t>108789375772</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>mug-kanu-150ml</t>
+  </si>
+  <si>
+    <t>mug-kanu-150ml-natural</t>
+  </si>
+  <si>
+    <t>28500</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>41831484258</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kora Tanapijak</t>
+  </si>
+  <si>
+    <t>441020593501</t>
+  </si>
+  <si>
+    <t>mug-kora-150ml</t>
+  </si>
+  <si>
+    <t>mug-kora-150ml-natural</t>
+  </si>
+  <si>
+    <t>29905865767</t>
+  </si>
+  <si>
+    <t>Mug Keramik 160ml - Cangkir Kopi Gelas Teh Mug Ocha | Gana Tanapijak</t>
+  </si>
+  <si>
+    <t>307674931496</t>
+  </si>
+  <si>
+    <t>mug-gana-160ml</t>
+  </si>
+  <si>
+    <t>mug-gana-160ml-biru</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>187666607210</t>
+  </si>
+  <si>
+    <t>mug-gana-160ml-orange</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>187666607211</t>
+  </si>
+  <si>
+    <t>Hitam</t>
+  </si>
+  <si>
+    <t>mug-gana-160ml-hitam</t>
+  </si>
+  <si>
+    <t>44611776154</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kuna Tanapijak</t>
+  </si>
+  <si>
+    <t>366020549670</t>
+  </si>
+  <si>
+    <t>Orange Percik</t>
+  </si>
+  <si>
+    <t>mug-kuna-150ml</t>
+  </si>
+  <si>
+    <t>mug-kuna-150ml-orangepercik</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>48011764693</t>
+  </si>
+  <si>
+    <t>Mug Keramik 300ml - Cangkir Teh Mug Teh Gelas Ocha | Kale Tanapijak</t>
+  </si>
+  <si>
+    <t>356020545685</t>
+  </si>
+  <si>
+    <t>Hijau</t>
+  </si>
+  <si>
+    <t>mug-kale-300ml</t>
+  </si>
+  <si>
+    <t>mug-kale-300ml-hijau</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>356020545684</t>
+  </si>
+  <si>
+    <t>mug-kale-300ml-orange</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>29679031083</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pila Tanapijak</t>
+  </si>
+  <si>
+    <t>215863315046</t>
+  </si>
+  <si>
+    <t>vas-pila</t>
+  </si>
+  <si>
+    <t>vas-pila-natural</t>
+  </si>
+  <si>
+    <t>24500</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>11758771408</t>
+  </si>
+  <si>
+    <t>Cangkir Keramik 300ml - Simpo Series - Tanapijak - cangkir teh gelas minum</t>
+  </si>
+  <si>
+    <t>103060586647</t>
+  </si>
+  <si>
+    <t>mug-simpo-300ml</t>
+  </si>
+  <si>
+    <t>mug-simpo-300ml-hitam</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>103060586648</t>
+  </si>
+  <si>
+    <t>mug-simpo-300ml-orange</t>
+  </si>
+  <si>
+    <t>103060586649</t>
+  </si>
+  <si>
+    <t>Cokelat</t>
+  </si>
+  <si>
+    <t>mug-simpo-300ml-cokelat</t>
+  </si>
+  <si>
+    <t>103060586650</t>
+  </si>
+  <si>
+    <t>mug-simpo-300ml-biru</t>
+  </si>
+  <si>
+    <t>12027152312</t>
+  </si>
+  <si>
+    <t>Extra Bubble Wrap untuk Packaging</t>
+  </si>
+  <si>
+    <t>300468166288</t>
+  </si>
+  <si>
+    <t>bubble-wrap</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>988</t>
+  </si>
+  <si>
+    <t>12927112884</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Namu Series - Tanapijak - gelas kopi cangkir teh</t>
+  </si>
+  <si>
+    <t>47514712533</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml-biru</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
+    <t>123786524908</t>
+  </si>
+  <si>
+    <t>Dark Orange</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml-darkorange</t>
+  </si>
+  <si>
+    <t>47514712530</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml-cokelat</t>
+  </si>
+  <si>
+    <t>47514712531</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml-hitam</t>
+  </si>
+  <si>
+    <t>47514712532</t>
+  </si>
+  <si>
+    <t>mug-namu-150ml-orange</t>
+  </si>
+  <si>
+    <t>16692646490</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Hias Pajangan - Ceramic Vase | Lema Tanapijak</t>
+  </si>
+  <si>
+    <t>213839065197</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vas-lema</t>
+  </si>
+  <si>
+    <t>vas-lema-putih</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>213839065198</t>
+  </si>
+  <si>
+    <t>Ocean Blue</t>
+  </si>
+  <si>
+    <t>vas-lema-biru</t>
+  </si>
+  <si>
+    <t>213839065199</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>vas-lema-kuning</t>
+  </si>
+  <si>
+    <t>18277724374</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Tara Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>194157684680</t>
+  </si>
+  <si>
+    <t>tungku-tara-5hole</t>
+  </si>
+  <si>
+    <t>tungku-tara-5hole-natural</t>
+  </si>
+  <si>
+    <t>18975922857</t>
+  </si>
+  <si>
+    <t>Piring Keramik - Piring Makan Snack - Snack Platter | Rumi Tanapijak</t>
+  </si>
+  <si>
+    <t>260468668965</t>
+  </si>
+  <si>
+    <t>Hijau - Cream</t>
+  </si>
+  <si>
+    <t>piring-rumi</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>19175928357</t>
+  </si>
+  <si>
+    <t>Gift Card - Kartu Ucapan A6 - Kartu Hadiah | Tanapijak</t>
+  </si>
+  <si>
+    <t>184036297333</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>gift-card</t>
+  </si>
+  <si>
+    <t>gift-card-a</t>
+  </si>
+  <si>
+    <t>3750</t>
+  </si>
+  <si>
+    <t>184036297331</t>
+  </si>
+  <si>
+    <t>Ramadhan 1</t>
+  </si>
+  <si>
+    <t>gift-card-b</t>
+  </si>
+  <si>
+    <t>184036297332</t>
+  </si>
+  <si>
+    <t>Ramadhan 2</t>
+  </si>
+  <si>
+    <t>gift-card-c</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>19375642362</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Kalana Tanapijak</t>
+  </si>
+  <si>
+    <t>218567670802</t>
+  </si>
+  <si>
+    <t>vas-kalana</t>
+  </si>
+  <si>
+    <t>vas-kalana-natural</t>
+  </si>
+  <si>
+    <t>37625</t>
+  </si>
+  <si>
+    <t>19591361325</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Oil Wax Burner Aroma Therapy | Hira Tanapijak</t>
+  </si>
+  <si>
+    <t>118967740690</t>
+  </si>
+  <si>
+    <t>tungku-hira</t>
+  </si>
+  <si>
+    <t>tungku-hira-natural</t>
+  </si>
+  <si>
+    <t>19646713258</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Karo Series - Tanapijak - gelas kopi cangkir teh</t>
+  </si>
+  <si>
+    <t>182358951255</t>
+  </si>
+  <si>
+    <t>Light Blue</t>
+  </si>
+  <si>
+    <t>mug-karo-150ml</t>
+  </si>
+  <si>
+    <t>mug-karo-150ml-biru</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>182358951252</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>mug-karo-150ml-cream</t>
+  </si>
+  <si>
+    <t>182358951253</t>
+  </si>
+  <si>
+    <t>Mocca</t>
+  </si>
+  <si>
+    <t>mug-karo-150ml-mocca</t>
+  </si>
+  <si>
+    <t>182358951254</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>mug-karo-150ml-hijau</t>
+  </si>
+  <si>
+    <t>19673107103</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Pata Tanapijak</t>
+  </si>
+  <si>
+    <t>280468094144</t>
+  </si>
+  <si>
+    <t>Biru - Cream</t>
+  </si>
+  <si>
+    <t>vas-pata</t>
+  </si>
+  <si>
+    <t>vas-pata-biru-cream</t>
+  </si>
+  <si>
+    <t>20500</t>
+  </si>
+  <si>
+    <t>20246723143</t>
+  </si>
+  <si>
+    <t>Mug Keramik 200ml - Hara Series - Tanapijak - gelas kopi cangkir teh</t>
+  </si>
+  <si>
+    <t>182359490601</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-putih</t>
+  </si>
+  <si>
+    <t>29500</t>
+  </si>
+  <si>
+    <t>182359490602</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-biru</t>
+  </si>
+  <si>
+    <t>182359490597</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-mocca</t>
+  </si>
+  <si>
+    <t>182359490598</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-cream</t>
+  </si>
+  <si>
+    <t>182359490599</t>
+  </si>
+  <si>
+    <t>Grape</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-ungu</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>182359490600</t>
+  </si>
+  <si>
+    <t>mug-hara-150ml-hijau</t>
+  </si>
+  <si>
+    <t>20461235683</t>
+  </si>
+  <si>
+    <t>DEFECT SALE B - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>165049647655</t>
+  </si>
+  <si>
+    <t>mug-defect-b</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>20561235974</t>
+  </si>
+  <si>
+    <t>DEFECT SALE C - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>117700199488</t>
+  </si>
+  <si>
+    <t>mug-defect-c</t>
+  </si>
+  <si>
+    <t>20882410618</t>
+  </si>
+  <si>
+    <t>Mug Keramik 270ml - Cangkir Teh Gelas Teh Mug Ocha | Kara Tanapijak</t>
+  </si>
+  <si>
+    <t>89408562665</t>
+  </si>
+  <si>
+    <t>mug-kara-270ml</t>
+  </si>
+  <si>
+    <t>mug-kara-270ml-cream</t>
+  </si>
+  <si>
+    <t>89408562664</t>
+  </si>
+  <si>
+    <t>mug-kara-270ml-cokelat</t>
+  </si>
+  <si>
+    <t>21074719071</t>
+  </si>
+  <si>
+    <t>Packing Kayu</t>
+  </si>
+  <si>
+    <t>79918452648</t>
+  </si>
+  <si>
+    <t>Kayu</t>
+  </si>
+  <si>
+    <t>packing-kayu</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>21346727654</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Nara Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>107443899158</t>
+  </si>
+  <si>
+    <t>tungku-nara</t>
+  </si>
+  <si>
+    <t>tungku-nara-cream</t>
+  </si>
+  <si>
+    <t>107443899159</t>
+  </si>
+  <si>
+    <t>tungku-nara-putih</t>
+  </si>
+  <si>
+    <t>117443799088</t>
+  </si>
+  <si>
+    <t>tungku-nara-hijau</t>
+  </si>
+  <si>
+    <t>193525539902</t>
+  </si>
+  <si>
+    <t>tungku-nara-natural</t>
+  </si>
+  <si>
+    <t>31500</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>21875629754</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Kanaka Tanapijak</t>
+  </si>
+  <si>
+    <t>243547239371</t>
+  </si>
+  <si>
+    <t>vas-kanaka</t>
+  </si>
+  <si>
+    <t>vas-kanaka-natural</t>
+  </si>
+  <si>
+    <t>35625</t>
+  </si>
+  <si>
+    <t>21961232835</t>
+  </si>
+  <si>
+    <t>DEFECT SALE A - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
+  </si>
+  <si>
+    <t>69168651563</t>
+  </si>
+  <si>
+    <t>mug-defect-a</t>
+  </si>
+  <si>
+    <t>22149833308</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Tanapijak</t>
+  </si>
+  <si>
+    <t>235467534967</t>
+  </si>
+  <si>
+    <t>Biru Garis</t>
+  </si>
+  <si>
+    <t>mug-kina-150ml</t>
+  </si>
+  <si>
+    <t>mug-kina-150ml-birugaris</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>235467534968</t>
+  </si>
+  <si>
+    <t>Biru Usap</t>
+  </si>
+  <si>
+    <t>mug-kina-150ml-biruusap</t>
+  </si>
+  <si>
+    <t>235467534966</t>
+  </si>
+  <si>
+    <t>Biru Percik</t>
+  </si>
+  <si>
+    <t>mug-kina-150ml-birupercik</t>
+  </si>
+  <si>
+    <t>22231551703</t>
+  </si>
+  <si>
+    <t>Hard Box - Box Hampers - Gift Box | Tanapijak</t>
+  </si>
+  <si>
+    <t>280468295909</t>
+  </si>
+  <si>
+    <t>Semi Gold</t>
+  </si>
+  <si>
+    <t>hampers-box</t>
+  </si>
+  <si>
+    <t>hampers-box-only</t>
+  </si>
+  <si>
+    <t>58000</t>
+  </si>
+  <si>
+    <t>22336652074</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kala Tanapijak</t>
+  </si>
+  <si>
+    <t>167781703735</t>
+  </si>
+  <si>
+    <t>mug-kala-150ml</t>
+  </si>
+  <si>
+    <t>mug-kala-150ml-hitam</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>108042713010</t>
+  </si>
+  <si>
+    <t>mug-kala-150ml-cokelat</t>
+  </si>
+  <si>
+    <t>108042713011</t>
+  </si>
+  <si>
+    <t>mug-kala-150ml-birutua</t>
+  </si>
+  <si>
+    <t>108042713012</t>
+  </si>
+  <si>
+    <t>Biru Muda</t>
+  </si>
+  <si>
+    <t>mug-kala-150ml-birumuda</t>
+  </si>
+  <si>
+    <t>22431547918</t>
+  </si>
+  <si>
+    <t>[HAMPERS] Tungku Aroma Terapi Set - Oil Wax Burner | Tanapijak</t>
+  </si>
+  <si>
+    <t>221221019710</t>
+  </si>
+  <si>
+    <t>hampers-tungku</t>
+  </si>
+  <si>
+    <t>hampers-tungku-set</t>
+  </si>
+  <si>
+    <t>126000</t>
+  </si>
+  <si>
+    <t>23049834550</t>
+  </si>
+  <si>
+    <t>Mug Keramik 300ml - Cangkir Teh Mug Teh Gelas Ocha | Kalu Tanapijak</t>
+  </si>
+  <si>
+    <t>235467536308</t>
+  </si>
+  <si>
+    <t>mug-kalu-300ml</t>
+  </si>
+  <si>
+    <t>mug-kalu-300ml-biru</t>
+  </si>
+  <si>
+    <t>235467536309</t>
+  </si>
+  <si>
+    <t>mug-kalu-300ml-hijau</t>
+  </si>
+  <si>
+    <t>176947547282</t>
+  </si>
+  <si>
+    <t>Abu-abu</t>
+  </si>
+  <si>
+    <t>mug-kalu-300ml-abu</t>
+  </si>
+  <si>
+    <t>23323734514</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pana Tanapijak</t>
+  </si>
+  <si>
+    <t>193839054188</t>
+  </si>
+  <si>
+    <t>vas-pana</t>
+  </si>
+  <si>
+    <t>vas-pana-putih</t>
+  </si>
+  <si>
+    <t>193839054189</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>vas-pana-cokelat</t>
+  </si>
+  <si>
+    <t>193839054190</t>
+  </si>
+  <si>
+    <t>Dark Blue</t>
+  </si>
+  <si>
+    <t>vas-pana-biru</t>
+  </si>
+  <si>
+    <t>23410401836</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Bara Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>203525766037</t>
+  </si>
+  <si>
+    <t>tungku-bara</t>
+  </si>
+  <si>
+    <t>tungku-bara-natural</t>
+  </si>
+  <si>
+    <t>35500</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>23564130680</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran D Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>176397300213</t>
+  </si>
+  <si>
+    <t>2 Mug</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-d</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-d-2mug</t>
+  </si>
+  <si>
+    <t>149900</t>
+  </si>
+  <si>
+    <t>176397300212</t>
+  </si>
+  <si>
+    <t>1 Mug</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-d-1mug</t>
+  </si>
+  <si>
+    <t>129900</t>
+  </si>
+  <si>
+    <t>23723732403</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Putu Tanapijak</t>
+  </si>
+  <si>
+    <t>270468114275</t>
+  </si>
+  <si>
+    <t>vas-putu</t>
+  </si>
+  <si>
+    <t>vas-putu-natural</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>23736647722</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Dara Tanapijak</t>
+  </si>
+  <si>
+    <t>165792194240</t>
+  </si>
+  <si>
+    <t>mug-dara-150ml</t>
+  </si>
+  <si>
+    <t>mug-dara-150ml-natural</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>23930727093</t>
+  </si>
+  <si>
+    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Carani Tanapijak</t>
+  </si>
+  <si>
+    <t>186130791482</t>
+  </si>
+  <si>
+    <t>vas-carani</t>
+  </si>
+  <si>
+    <t>vas-carani-natural</t>
+  </si>
+  <si>
+    <t>23931542009</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Gelas Ocha Teh Kopi - Mug Ocha | Soja Tanapijak</t>
+  </si>
+  <si>
+    <t>146717259883</t>
+  </si>
+  <si>
+    <t>mug-soja-150ml</t>
+  </si>
+  <si>
+    <t>mug-soja-150ml-natural</t>
+  </si>
+  <si>
+    <t>22500</t>
+  </si>
+  <si>
+    <t>24170867147</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran J Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>98895036732</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-j</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-j-2mug</t>
+  </si>
+  <si>
+    <t>179900</t>
+  </si>
+  <si>
+    <t>98895036731</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-j-1mug</t>
+  </si>
+  <si>
+    <t>24369445579</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran E Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>226176027849</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-e</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-e-1mug</t>
+  </si>
+  <si>
+    <t>226176027850</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-e-2mug</t>
+  </si>
+  <si>
+    <t>24629381092</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Tara 3 Hole Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>207494478532</t>
+  </si>
+  <si>
+    <t>tungku-tara-3hole</t>
+  </si>
+  <si>
+    <t>tungku-tara-3hole-natural</t>
+  </si>
+  <si>
+    <t>24669442533</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran G Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>236176030180</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-g</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-g-1mug</t>
+  </si>
+  <si>
+    <t>236176030181</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-g-2mug</t>
+  </si>
+  <si>
+    <t>24769440157</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran F Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>79407129344</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-f</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-f-1mug</t>
+  </si>
+  <si>
+    <t>79407129345</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-f-2mug</t>
+  </si>
+  <si>
+    <t>24819440377</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran H Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>245551263292</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-h</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-h-1mug</t>
+  </si>
+  <si>
+    <t>245551263293</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-h-2mug</t>
+  </si>
+  <si>
+    <t>25170856475</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran I Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>194997161152</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-i</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-i-2mug</t>
+  </si>
+  <si>
+    <t>194997161151</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-i-1mug</t>
+  </si>
+  <si>
+    <t>25219436428</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran B Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>222638914766</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-b</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-b-2mug</t>
+  </si>
+  <si>
+    <t>222638914765</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-b-1mug</t>
+  </si>
+  <si>
+    <t>25269436182</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran A Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>118323220391</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-a</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-a-1mug</t>
+  </si>
+  <si>
+    <t>118323220390</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-a-2mug</t>
+  </si>
+  <si>
+    <t>25470855122</t>
+  </si>
+  <si>
+    <t>Mug Keramik 350ml - Cangkir Teh Gelas Teh Mug Ocha | Rana Tanapijak</t>
+  </si>
+  <si>
+    <t>240538064971</t>
+  </si>
+  <si>
+    <t>mug-rana-350ml</t>
+  </si>
+  <si>
+    <t>mug-rana-350ml-biru</t>
+  </si>
+  <si>
+    <t>34500</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>240538064972</t>
+  </si>
+  <si>
+    <t>mug-rana-350ml-cream</t>
+  </si>
+  <si>
+    <t>233316677991</t>
+  </si>
+  <si>
+    <t>mug-rana-350ml-natural</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>25569437226</t>
+  </si>
+  <si>
+    <t>Hampers Lebaran C Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
+  </si>
+  <si>
+    <t>245551189107</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-c</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-c-1mug</t>
+  </si>
+  <si>
+    <t>245551189108</t>
+  </si>
+  <si>
+    <t>hampers-lebaran-c-2mug</t>
+  </si>
+  <si>
+    <t>25629379723</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Orange Tanapijak</t>
+  </si>
+  <si>
+    <t>245792042693</t>
+  </si>
+  <si>
+    <t>mug-kina-150ml-orange</t>
+  </si>
+  <si>
+    <t>26155863783</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kaja Tanapijak</t>
+  </si>
+  <si>
+    <t>215255320485</t>
+  </si>
+  <si>
+    <t>mug-kaja-150ml</t>
+  </si>
+  <si>
+    <t>mug-kaja-150ml-hijau</t>
+  </si>
+  <si>
+    <t>215255320484</t>
+  </si>
+  <si>
+    <t>mug-kaja-150ml-orange</t>
+  </si>
+  <si>
+    <t>26512555118</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Sera Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>246678607213</t>
+  </si>
+  <si>
+    <t>tungku-sera</t>
+  </si>
+  <si>
+    <t>tungku-sera-natural</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>27443417088</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kila Tanapijak</t>
+  </si>
+  <si>
+    <t>277095072360</t>
+  </si>
+  <si>
+    <t>Cokelat Percik</t>
+  </si>
+  <si>
+    <t>mug-kila-150ml</t>
+  </si>
+  <si>
+    <t>mug-kila-150ml-cokelat</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>28179025918</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pala Tanapijak</t>
+  </si>
+  <si>
+    <t>223914442988</t>
+  </si>
+  <si>
+    <t>vas-pala</t>
+  </si>
+  <si>
+    <t>vas-pala-natural</t>
+  </si>
+  <si>
+    <t>26000</t>
+  </si>
+  <si>
+    <t>28529040396</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pota Tanapijak</t>
+  </si>
+  <si>
+    <t>149059652704</t>
+  </si>
+  <si>
+    <t>vas-pota</t>
+  </si>
+  <si>
+    <t>vas-pota-natural</t>
+  </si>
+  <si>
+    <t>28779031134</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pusa Tanapijak</t>
+  </si>
+  <si>
+    <t>195863329858</t>
+  </si>
+  <si>
+    <t>vas-pusa</t>
+  </si>
+  <si>
+    <t>vas-pusa-natural</t>
+  </si>
+  <si>
+    <t>23500</t>
+  </si>
+  <si>
+    <t>29029019720</t>
+  </si>
+  <si>
+    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pega Tanapijak</t>
+  </si>
+  <si>
+    <t>99774474219</t>
+  </si>
+  <si>
+    <t>vas-pega</t>
+  </si>
+  <si>
+    <t>vas-pega-natural</t>
+  </si>
+  <si>
+    <t>41225847259</t>
+  </si>
+  <si>
+    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kiro Tanapijak</t>
+  </si>
+  <si>
+    <t>425021790604</t>
+  </si>
+  <si>
+    <t>mug-kiro-150ml</t>
+  </si>
+  <si>
+    <t>mug-kiro-150ml-cokelat</t>
+  </si>
+  <si>
+    <t>29324940474</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Goya Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>198186989036</t>
+  </si>
+  <si>
+    <t>tungku-goya</t>
+  </si>
+  <si>
+    <t>tungku-goya-natural</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>29755865909</t>
+  </si>
+  <si>
+    <t>Mug Keramik 230ml - Cangkir Kopi Gelas Teh Mug Ocha | Giri Tanapijak</t>
+  </si>
+  <si>
+    <t>246234835473</t>
+  </si>
+  <si>
+    <t>Hijau - Putih</t>
+  </si>
+  <si>
+    <t>mug-giri-230ml</t>
+  </si>
+  <si>
+    <t>mug-giri-230ml-hijau-putih</t>
+  </si>
+  <si>
+    <t>246234835470</t>
+  </si>
+  <si>
+    <t>Cokelat - Hijau</t>
+  </si>
+  <si>
+    <t>mug-giri-230ml-cokelat-hijau</t>
+  </si>
+  <si>
+    <t>246234835471</t>
+  </si>
+  <si>
+    <t>Cokelat - Biru</t>
+  </si>
+  <si>
+    <t>mug-giri-230ml-cokelat-biru</t>
+  </si>
+  <si>
+    <t>246234835472</t>
+  </si>
+  <si>
+    <t>Cokelat - Putih</t>
+  </si>
+  <si>
+    <t>mug-giri-230ml-cokelat-putih</t>
+  </si>
+  <si>
+    <t>40280967831</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Sira Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>310934934606</t>
+  </si>
+  <si>
+    <t>tungku-sira</t>
+  </si>
+  <si>
+    <t>tungku-sira-natural</t>
+  </si>
+  <si>
+    <t>33500</t>
+  </si>
+  <si>
+    <t>41606623527</t>
+  </si>
+  <si>
+    <t>Mug Keramik 110ml - Cangkir Kopi Gelas Teh Mug Ocha | Nako Tanapijak</t>
+  </si>
+  <si>
+    <t>177221833107</t>
+  </si>
+  <si>
+    <t>mug-nako-110ml</t>
+  </si>
+  <si>
+    <t>mug-nako-110ml-hijau</t>
+  </si>
+  <si>
+    <t>206141739564</t>
+  </si>
+  <si>
+    <t>mug-nako-110ml-orange</t>
+  </si>
+  <si>
+    <t>177221833105</t>
+  </si>
+  <si>
+    <t>mug-nako-110ml-birumuda</t>
+  </si>
+  <si>
+    <t>177221833106</t>
+  </si>
+  <si>
+    <t>Biru Tua</t>
+  </si>
+  <si>
+    <t>mug-nako-110ml-birutua</t>
+  </si>
+  <si>
+    <t>44810684513</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Sora Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>440934248626</t>
+  </si>
+  <si>
+    <t>tungku-sora</t>
+  </si>
+  <si>
+    <t>tungku-sora-natural</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>48710320194</t>
+  </si>
+  <si>
+    <t>Mug Keramik 110ml - Cangkir Kopi Gelas Teh Mug Ocha | Niko Tanapijak</t>
+  </si>
+  <si>
+    <t>400904877375</t>
+  </si>
+  <si>
+    <t>mug-niko-110ml</t>
+  </si>
+  <si>
+    <t>mug-niko-110ml-natural</t>
+  </si>
+  <si>
+    <t>49300261987</t>
+  </si>
+  <si>
+    <t>Mug Keramik 280ml - Cangkir Kopi Gelas Teh Mug Ocha Gelas Keramik | Dira Tanapijak</t>
+  </si>
+  <si>
+    <t>405022224555</t>
+  </si>
+  <si>
+    <t>Putih - Cokelat</t>
+  </si>
+  <si>
+    <t>mug-dira-280ml</t>
+  </si>
+  <si>
+    <t>mug-dira-280ml-cokelat</t>
+  </si>
+  <si>
+    <t>53510669144</t>
+  </si>
+  <si>
+    <t>Tungku Aroma Terapi - Sura Series - Tanapijak - Lilin Essential Oil</t>
+  </si>
+  <si>
+    <t>350934300665</t>
+  </si>
+  <si>
+    <t>tungku-sura</t>
+  </si>
+  <si>
+    <t>tungku-sura-natural</t>
+  </si>
+  <si>
+    <t>56100240517</t>
+  </si>
+  <si>
+    <t>Mug Keramik 230ml - Cangkir Kopi Gelas Teh Mug Ocha | Gari Tanapijak</t>
+  </si>
+  <si>
+    <t>355021669817</t>
+  </si>
+  <si>
+    <t>mug-gari-230ml</t>
+  </si>
+  <si>
+    <t>mug-gari-230ml-biru</t>
+  </si>
+  <si>
+    <t>355021669818</t>
+  </si>
+  <si>
+    <t>mug-gari-230ml-putih</t>
   </si>
   <si>
     <t>58060293719</t>
@@ -159,1363 +1767,7 @@
     <t>Pink</t>
   </si>
   <si>
-    <t>mugkinapink</t>
-  </si>
-  <si>
-    <t>28500</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>56100240517</t>
-  </si>
-  <si>
-    <t>Mug Keramik 230ml - Cangkir Kopi Gelas Teh Mug Ocha | Gari Tanapijak</t>
-  </si>
-  <si>
-    <t>355021669817</t>
-  </si>
-  <si>
-    <t>Cokelat - Biru</t>
-  </si>
-  <si>
-    <t>muggari</t>
-  </si>
-  <si>
-    <t>muggaribiru</t>
-  </si>
-  <si>
-    <t>31000</t>
-  </si>
-  <si>
-    <t>00</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>355021669818</t>
-  </si>
-  <si>
-    <t>Cokelat - Putih</t>
-  </si>
-  <si>
-    <t>muggariputih</t>
-  </si>
-  <si>
-    <t>53510669144</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Sura Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>350934300665</t>
-  </si>
-  <si>
-    <t>Natural</t>
-  </si>
-  <si>
-    <t>tungkusura</t>
-  </si>
-  <si>
-    <t>tungkusuranatural</t>
-  </si>
-  <si>
-    <t>33500</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>49300261987</t>
-  </si>
-  <si>
-    <t>Mug Keramik 280ml - Cangkir Kopi Gelas Teh Mug Ocha Gelas Keramik | Dira Tanapijak</t>
-  </si>
-  <si>
-    <t>405022224555</t>
-  </si>
-  <si>
-    <t>Putih - Cokelat</t>
-  </si>
-  <si>
-    <t>mugdira</t>
-  </si>
-  <si>
-    <t>mugdiracokelat</t>
-  </si>
-  <si>
-    <t>35500</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>48710320194</t>
-  </si>
-  <si>
-    <t>Mug Keramik 110ml - Cangkir Kopi Gelas Teh Mug Ocha | Niko Tanapijak</t>
-  </si>
-  <si>
-    <t>400904877375</t>
-  </si>
-  <si>
-    <t>mugniko</t>
-  </si>
-  <si>
-    <t>mugnikonatural</t>
-  </si>
-  <si>
-    <t>26500</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>44810684513</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Sora Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>440934248626</t>
-  </si>
-  <si>
-    <t>tungkusora</t>
-  </si>
-  <si>
-    <t>tungkusoranatural</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>41606623527</t>
-  </si>
-  <si>
-    <t>Mug Keramik 110ml - Cangkir Kopi Gelas Teh Mug Ocha | Nako Tanapijak</t>
-  </si>
-  <si>
-    <t>177221833106</t>
-  </si>
-  <si>
-    <t>Biru Tua</t>
-  </si>
-  <si>
-    <t>mugnako</t>
-  </si>
-  <si>
-    <t>mugnakobirutua</t>
-  </si>
-  <si>
-    <t>177221833107</t>
-  </si>
-  <si>
-    <t>Hijau</t>
-  </si>
-  <si>
-    <t>mugnakohijau</t>
-  </si>
-  <si>
-    <t>206141739564</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>mugnakoorange</t>
-  </si>
-  <si>
-    <t>177221833105</t>
-  </si>
-  <si>
-    <t>Biru Muda</t>
-  </si>
-  <si>
-    <t>mugnakobirumuda</t>
-  </si>
-  <si>
-    <t>41225847259</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kiro Tanapijak</t>
-  </si>
-  <si>
-    <t>425021790604</t>
-  </si>
-  <si>
-    <t>Cokelat</t>
-  </si>
-  <si>
-    <t>mugkiro</t>
-  </si>
-  <si>
-    <t>mugkirocokelat</t>
-  </si>
-  <si>
-    <t>40280967831</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Sira Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>310934934606</t>
-  </si>
-  <si>
-    <t>tungkusira</t>
-  </si>
-  <si>
-    <t>tungkusiranatural</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>29905865767</t>
-  </si>
-  <si>
-    <t>Mug Keramik 160ml - Cangkir Kopi Gelas Teh Mug Ocha | Gana Tanapijak</t>
-  </si>
-  <si>
-    <t>187666607211</t>
-  </si>
-  <si>
-    <t>Hitam</t>
-  </si>
-  <si>
-    <t>muggana</t>
-  </si>
-  <si>
-    <t>mugganahitam</t>
-  </si>
-  <si>
-    <t>187666607210</t>
-  </si>
-  <si>
-    <t>mugganaorange</t>
-  </si>
-  <si>
-    <t>29755865909</t>
-  </si>
-  <si>
-    <t>Mug Keramik 230ml - Cangkir Kopi Gelas Teh Mug Ocha | Giri Tanapijak</t>
-  </si>
-  <si>
-    <t>246234835470</t>
-  </si>
-  <si>
-    <t>Cokelat - Hijau</t>
-  </si>
-  <si>
-    <t>muggiri</t>
-  </si>
-  <si>
-    <t>muggiricoklathijau</t>
-  </si>
-  <si>
-    <t>246234835471</t>
-  </si>
-  <si>
-    <t>muggiricoklatbiru</t>
-  </si>
-  <si>
-    <t>246234835472</t>
-  </si>
-  <si>
-    <t>muggiricoklatputih</t>
-  </si>
-  <si>
-    <t>246234835473</t>
-  </si>
-  <si>
-    <t>Hijau - Putih</t>
-  </si>
-  <si>
-    <t>muggirihijauputih</t>
-  </si>
-  <si>
-    <t>29679031083</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pila Tanapijak</t>
-  </si>
-  <si>
-    <t>215863315046</t>
-  </si>
-  <si>
-    <t>vaspila</t>
-  </si>
-  <si>
-    <t>vaspilanatural</t>
-  </si>
-  <si>
-    <t>24500</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>29324940474</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Goya Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>198186989036</t>
-  </si>
-  <si>
-    <t>tungkugoya</t>
-  </si>
-  <si>
-    <t>tungkugoyanatural</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>29029019720</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pega Tanapijak</t>
-  </si>
-  <si>
-    <t>99774474219</t>
-  </si>
-  <si>
-    <t>vaspega</t>
-  </si>
-  <si>
-    <t>vaspeganatural</t>
-  </si>
-  <si>
-    <t>29500</t>
-  </si>
-  <si>
-    <t>28779031134</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pusa Tanapijak</t>
-  </si>
-  <si>
-    <t>195863329858</t>
-  </si>
-  <si>
-    <t>vaspusa</t>
-  </si>
-  <si>
-    <t>vaspusanatural</t>
-  </si>
-  <si>
-    <t>23500</t>
-  </si>
-  <si>
-    <t>28529040396</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pota Tanapijak</t>
-  </si>
-  <si>
-    <t>149059652704</t>
-  </si>
-  <si>
-    <t>vaspota</t>
-  </si>
-  <si>
-    <t>vaspotanatural</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>28179025918</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pala Tanapijak</t>
-  </si>
-  <si>
-    <t>223914442988</t>
-  </si>
-  <si>
-    <t>vaspala</t>
-  </si>
-  <si>
-    <t>vaspalanatural</t>
-  </si>
-  <si>
-    <t>26000</t>
-  </si>
-  <si>
-    <t>27443417088</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kila Tanapijak</t>
-  </si>
-  <si>
-    <t>277095072360</t>
-  </si>
-  <si>
-    <t>Cokelat Percik</t>
-  </si>
-  <si>
-    <t>mugkila</t>
-  </si>
-  <si>
-    <t>mugkilacokelat</t>
-  </si>
-  <si>
-    <t>26512555118</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Sera Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>246678607213</t>
-  </si>
-  <si>
-    <t>tungkusera</t>
-  </si>
-  <si>
-    <t>tungkuseranatural</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>26155863783</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kaja Tanapijak</t>
-  </si>
-  <si>
-    <t>215255320485</t>
-  </si>
-  <si>
-    <t>mugkaja</t>
-  </si>
-  <si>
-    <t>mugkajahijau</t>
-  </si>
-  <si>
-    <t>215255320484</t>
-  </si>
-  <si>
-    <t>mugkajaorange</t>
-  </si>
-  <si>
-    <t>25629379723</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Orange Tanapijak</t>
-  </si>
-  <si>
-    <t>245792042693</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>25569437226</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran C Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>245551189107</t>
-  </si>
-  <si>
-    <t>1 Mug</t>
-  </si>
-  <si>
-    <t>129900</t>
-  </si>
-  <si>
-    <t>245551189108</t>
-  </si>
-  <si>
-    <t>2 Mug</t>
-  </si>
-  <si>
-    <t>149900</t>
-  </si>
-  <si>
-    <t>25470855122</t>
-  </si>
-  <si>
-    <t>Mug Keramik 350ml - Cangkir Teh Gelas Teh Mug Ocha | Rana Tanapijak</t>
-  </si>
-  <si>
-    <t>233316677991</t>
-  </si>
-  <si>
-    <t>mugrana</t>
-  </si>
-  <si>
-    <t>mugrananatural</t>
-  </si>
-  <si>
-    <t>34500</t>
-  </si>
-  <si>
-    <t>240538064971</t>
-  </si>
-  <si>
-    <t>Biru</t>
-  </si>
-  <si>
-    <t>mugranabiru</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>240538064972</t>
-  </si>
-  <si>
-    <t>Cream</t>
-  </si>
-  <si>
-    <t>mugranacream</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>25269436182</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran A Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>118323220391</t>
-  </si>
-  <si>
-    <t>118323220390</t>
-  </si>
-  <si>
-    <t>25219436428</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran B Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>222638914765</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>222638914766</t>
-  </si>
-  <si>
-    <t>25170856475</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran I Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>194997161151</t>
-  </si>
-  <si>
-    <t>194997161152</t>
-  </si>
-  <si>
-    <t>179900</t>
-  </si>
-  <si>
-    <t>24819440377</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran H Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>245551263292</t>
-  </si>
-  <si>
-    <t>245551263293</t>
-  </si>
-  <si>
-    <t>24769440157</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran F Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>79407129344</t>
-  </si>
-  <si>
-    <t>79407129345</t>
-  </si>
-  <si>
-    <t>24669442533</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran G Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>236176030180</t>
-  </si>
-  <si>
-    <t>236176030181</t>
-  </si>
-  <si>
-    <t>24629381092</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Tara 3 Hole Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>207494478532</t>
-  </si>
-  <si>
-    <t>tungkutara3</t>
-  </si>
-  <si>
-    <t>tungkutara3natural</t>
-  </si>
-  <si>
-    <t>24369445579</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran E Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>226176027849</t>
-  </si>
-  <si>
-    <t>226176027850</t>
-  </si>
-  <si>
-    <t>24170867147</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran J Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>98895036731</t>
-  </si>
-  <si>
-    <t>98895036732</t>
-  </si>
-  <si>
-    <t>23931542009</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Gelas Ocha Teh Kopi - Mug Ocha | Soja Tanapijak</t>
-  </si>
-  <si>
-    <t>146717259883</t>
-  </si>
-  <si>
-    <t>22500</t>
-  </si>
-  <si>
-    <t>23930727093</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Carani Tanapijak</t>
-  </si>
-  <si>
-    <t>186130791482</t>
-  </si>
-  <si>
-    <t>vascarani</t>
-  </si>
-  <si>
-    <t>vascaraninatural</t>
-  </si>
-  <si>
-    <t>37625</t>
-  </si>
-  <si>
-    <t>23736647722</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Dara Tanapijak</t>
-  </si>
-  <si>
-    <t>165792194240</t>
-  </si>
-  <si>
-    <t>23000</t>
-  </si>
-  <si>
-    <t>23723732403</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Putu Tanapijak</t>
-  </si>
-  <si>
-    <t>270468114275</t>
-  </si>
-  <si>
-    <t>Biru - Cream</t>
-  </si>
-  <si>
-    <t>vasputu</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>23564130680</t>
-  </si>
-  <si>
-    <t>Hampers Lebaran D Set Mug x Cookies by Alana Brownies x Tea by Hondje</t>
-  </si>
-  <si>
-    <t>176397300212</t>
-  </si>
-  <si>
-    <t>176397300213</t>
-  </si>
-  <si>
-    <t>23410401836</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Bara Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>203525766037</t>
-  </si>
-  <si>
-    <t>tungkubara</t>
-  </si>
-  <si>
-    <t>tungkubaranatural</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>23323734514</t>
-  </si>
-  <si>
-    <t>Vas Bunga Keramik - Vas Tanaman Hias - Ceramic Vase | Pana Tanapijak</t>
-  </si>
-  <si>
-    <t>193839054190</t>
-  </si>
-  <si>
-    <t>Dark Blue</t>
-  </si>
-  <si>
-    <t>vaspana</t>
-  </si>
-  <si>
-    <t>vaspanabiru</t>
-  </si>
-  <si>
-    <t>20500</t>
-  </si>
-  <si>
-    <t>193839054188</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>vaspanaputih</t>
-  </si>
-  <si>
-    <t>193839054189</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>vaspanacoklat</t>
-  </si>
-  <si>
-    <t>23049834550</t>
-  </si>
-  <si>
-    <t>Mug Keramik 300ml - Cangkir Teh Mug Teh Gelas Ocha | Kalu Tanapijak</t>
-  </si>
-  <si>
-    <t>176947547282</t>
-  </si>
-  <si>
-    <t>Abu-abu</t>
-  </si>
-  <si>
-    <t>mugkalu</t>
-  </si>
-  <si>
-    <t>mugkaluabu</t>
-  </si>
-  <si>
-    <t>235467536308</t>
-  </si>
-  <si>
-    <t>mugkalubiru</t>
-  </si>
-  <si>
-    <t>235467536309</t>
-  </si>
-  <si>
-    <t>mugkaluhijau</t>
-  </si>
-  <si>
-    <t>22431547918</t>
-  </si>
-  <si>
-    <t>[HAMPERS] Tungku Aroma Terapi Set - Oil Wax Burner | Tanapijak</t>
-  </si>
-  <si>
-    <t>221221019710</t>
-  </si>
-  <si>
-    <t>126000</t>
-  </si>
-  <si>
-    <t>22336652074</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kala Tanapijak</t>
-  </si>
-  <si>
-    <t>108042713010</t>
-  </si>
-  <si>
-    <t>mugkala</t>
-  </si>
-  <si>
-    <t>mugkalacoklat</t>
-  </si>
-  <si>
-    <t>108042713011</t>
-  </si>
-  <si>
-    <t>mugkalabiru</t>
-  </si>
-  <si>
-    <t>108042713012</t>
-  </si>
-  <si>
-    <t>mugkalabirumuda</t>
-  </si>
-  <si>
-    <t>167781703735</t>
-  </si>
-  <si>
-    <t>mugkalahitam</t>
-  </si>
-  <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>22231551703</t>
-  </si>
-  <si>
-    <t>Hard Box - Box Hampers - Gift Box | Tanapijak</t>
-  </si>
-  <si>
-    <t>280468295909</t>
-  </si>
-  <si>
-    <t>Semi Gold</t>
-  </si>
-  <si>
-    <t>boxhampers</t>
-  </si>
-  <si>
-    <t>58000</t>
-  </si>
-  <si>
-    <t>22149833308</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Cangkir Kopi Gelas Teh Mug Ocha | Kina Tanapijak</t>
-  </si>
-  <si>
-    <t>235467534966</t>
-  </si>
-  <si>
-    <t>Biru Percik</t>
-  </si>
-  <si>
-    <t>mugkina</t>
-  </si>
-  <si>
-    <t>mugkinapercik</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>235467534967</t>
-  </si>
-  <si>
-    <t>Biru Garis</t>
-  </si>
-  <si>
-    <t>mugkinagaris</t>
-  </si>
-  <si>
-    <t>235467534968</t>
-  </si>
-  <si>
-    <t>Biru Usap</t>
-  </si>
-  <si>
-    <t>mugkinausap</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>21961232835</t>
-  </si>
-  <si>
-    <t>DEFECT SALE A - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>69168651563</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>21875629754</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Kanaka Tanapijak</t>
-  </si>
-  <si>
-    <t>243547239371</t>
-  </si>
-  <si>
-    <t>vaskanaka</t>
-  </si>
-  <si>
-    <t>vaskanakanatural</t>
-  </si>
-  <si>
-    <t>35625</t>
-  </si>
-  <si>
-    <t>21346727654</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Nara Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>107443899159</t>
-  </si>
-  <si>
-    <t>tungkunara</t>
-  </si>
-  <si>
-    <t>tungkunarawhite</t>
-  </si>
-  <si>
-    <t>117443799088</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>tungkunaragreen</t>
-  </si>
-  <si>
-    <t>193525539902</t>
-  </si>
-  <si>
-    <t>tungkunaranatural</t>
-  </si>
-  <si>
-    <t>31500</t>
-  </si>
-  <si>
-    <t>107443899158</t>
-  </si>
-  <si>
-    <t>tungkunaracream</t>
-  </si>
-  <si>
-    <t>21074719071</t>
-  </si>
-  <si>
-    <t>Packing Kayu</t>
-  </si>
-  <si>
-    <t>79918452648</t>
-  </si>
-  <si>
-    <t>Kayu</t>
-  </si>
-  <si>
-    <t>packingkayu</t>
-  </si>
-  <si>
-    <t>75000</t>
-  </si>
-  <si>
-    <t>993</t>
-  </si>
-  <si>
-    <t>20882410618</t>
-  </si>
-  <si>
-    <t>Mug Keramik 270ml - Cangkir Teh Gelas Teh Mug Ocha | Kara Tanapijak</t>
-  </si>
-  <si>
-    <t>89408562664</t>
-  </si>
-  <si>
-    <t>mugkara</t>
-  </si>
-  <si>
-    <t>mugkaracoklat</t>
-  </si>
-  <si>
-    <t>89408562665</t>
-  </si>
-  <si>
-    <t>mugkaracream</t>
-  </si>
-  <si>
-    <t>20561235974</t>
-  </si>
-  <si>
-    <t>DEFECT SALE C - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>117700199488</t>
-  </si>
-  <si>
-    <t>20461235683</t>
-  </si>
-  <si>
-    <t>DEFECT SALE B - 3pcs Mug - 150ml - Tanapijak - gelas cangkir</t>
-  </si>
-  <si>
-    <t>165049647655</t>
-  </si>
-  <si>
-    <t>20246723143</t>
-  </si>
-  <si>
-    <t>Mug Keramik 200ml - Hara Series - Tanapijak - gelas kopi cangkir teh</t>
-  </si>
-  <si>
-    <t>182359490597</t>
-  </si>
-  <si>
-    <t>Mocca</t>
-  </si>
-  <si>
-    <t>mughara</t>
-  </si>
-  <si>
-    <t>mugharamocca</t>
-  </si>
-  <si>
-    <t>182359490598</t>
-  </si>
-  <si>
-    <t>mugharacream</t>
-  </si>
-  <si>
-    <t>182359490599</t>
-  </si>
-  <si>
-    <t>Grape</t>
-  </si>
-  <si>
-    <t>mugharaungu</t>
-  </si>
-  <si>
-    <t>182359490600</t>
-  </si>
-  <si>
-    <t>mugharahijau</t>
-  </si>
-  <si>
-    <t>182359490601</t>
-  </si>
-  <si>
-    <t>mugharaputih</t>
-  </si>
-  <si>
-    <t>182359490602</t>
-  </si>
-  <si>
-    <t>Light Blue</t>
-  </si>
-  <si>
-    <t>mugharabiru</t>
-  </si>
-  <si>
-    <t>19673107103</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Pata Tanapijak</t>
-  </si>
-  <si>
-    <t>280468094144</t>
-  </si>
-  <si>
-    <t>vaspata</t>
-  </si>
-  <si>
-    <t>19646713258</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Karo Series - Tanapijak - gelas kopi cangkir teh</t>
-  </si>
-  <si>
-    <t>182358951252</t>
-  </si>
-  <si>
-    <t>mugkaro</t>
-  </si>
-  <si>
-    <t>mugkarocream</t>
-  </si>
-  <si>
-    <t>182358951253</t>
-  </si>
-  <si>
-    <t>mugkaromocca</t>
-  </si>
-  <si>
-    <t>182358951254</t>
-  </si>
-  <si>
-    <t>mugkarogreen</t>
-  </si>
-  <si>
-    <t>182358951255</t>
-  </si>
-  <si>
-    <t>mugkarobiru</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>19591361325</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Oil Wax Burner Aroma Therapy | Hira Tanapijak</t>
-  </si>
-  <si>
-    <t>118967740690</t>
-  </si>
-  <si>
-    <t>tungkuhira</t>
-  </si>
-  <si>
-    <t>tungkuhiranatural</t>
-  </si>
-  <si>
-    <t>19375642362</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Tanaman Hias - Ceramic Pot | Kalana Tanapijak</t>
-  </si>
-  <si>
-    <t>218567670802</t>
-  </si>
-  <si>
-    <t>vaskalana</t>
-  </si>
-  <si>
-    <t>vaskalananatural</t>
-  </si>
-  <si>
-    <t>19175928357</t>
-  </si>
-  <si>
-    <t>Gift Card - Kartu Ucapan A6 - Kartu Hadiah | Tanapijak</t>
-  </si>
-  <si>
-    <t>184036297331</t>
-  </si>
-  <si>
-    <t>Ramadhan 1</t>
-  </si>
-  <si>
-    <t>3750</t>
-  </si>
-  <si>
-    <t>184036297332</t>
-  </si>
-  <si>
-    <t>Ramadhan 2</t>
-  </si>
-  <si>
-    <t>184036297333</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>18975922857</t>
-  </si>
-  <si>
-    <t>Piring Keramik - Piring Makan Snack - Snack Platter | Rumi Tanapijak</t>
-  </si>
-  <si>
-    <t>260468668965</t>
-  </si>
-  <si>
-    <t>Hijau - Cream</t>
-  </si>
-  <si>
-    <t>piringrumi</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>18277724374</t>
-  </si>
-  <si>
-    <t>Tungku Aroma Terapi - Tara Series - Tanapijak - Lilin Essential Oil</t>
-  </si>
-  <si>
-    <t>194157684680</t>
-  </si>
-  <si>
-    <t>tungkutara5</t>
-  </si>
-  <si>
-    <t>tungkutara5natural</t>
-  </si>
-  <si>
-    <t>16692646490</t>
-  </si>
-  <si>
-    <t>Pot Bunga Keramik - Vas Hias Pajangan - Ceramic Vase | Lema Tanapijak</t>
-  </si>
-  <si>
-    <t>213839065199</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>vaslema</t>
-  </si>
-  <si>
-    <t>vaslemakuning</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>213839065197</t>
-  </si>
-  <si>
-    <t>vaslemaputih</t>
-  </si>
-  <si>
-    <t>213839065198</t>
-  </si>
-  <si>
-    <t>Ocean Blue</t>
-  </si>
-  <si>
-    <t>vaslemabiru</t>
-  </si>
-  <si>
-    <t>12927112884</t>
-  </si>
-  <si>
-    <t>Mug Keramik 150ml - Namu Series - Tanapijak - gelas kopi cangkir teh</t>
-  </si>
-  <si>
-    <t>47514712530</t>
-  </si>
-  <si>
-    <t>Namu Cokelat</t>
-  </si>
-  <si>
-    <t>13000</t>
-  </si>
-  <si>
-    <t>47514712531</t>
-  </si>
-  <si>
-    <t>Namu Hitam</t>
-  </si>
-  <si>
-    <t>47514712532</t>
-  </si>
-  <si>
-    <t>Namu Orange</t>
-  </si>
-  <si>
-    <t>47514712533</t>
-  </si>
-  <si>
-    <t>Namu Biru</t>
-  </si>
-  <si>
-    <t>123786524908</t>
-  </si>
-  <si>
-    <t>Dark Orange</t>
-  </si>
-  <si>
-    <t>Namu Dark Orange</t>
-  </si>
-  <si>
-    <t>12027152312</t>
-  </si>
-  <si>
-    <t>Extra Bubble Wrap untuk Packaging</t>
-  </si>
-  <si>
-    <t>300468166288</t>
-  </si>
-  <si>
-    <t>bubblewrap</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>934</t>
-  </si>
-  <si>
-    <t>11758771408</t>
-  </si>
-  <si>
-    <t>Cangkir Keramik 300ml - Simpo Series - Tanapijak - cangkir teh gelas minum</t>
-  </si>
-  <si>
-    <t>103060586648</t>
-  </si>
-  <si>
-    <t>Simpo Orange</t>
-  </si>
-  <si>
-    <t>19000</t>
-  </si>
-  <si>
-    <t>103060586649</t>
-  </si>
-  <si>
-    <t>Simpo Cokelat</t>
-  </si>
-  <si>
-    <t>103060586650</t>
-  </si>
-  <si>
-    <t>Simpo Biru</t>
-  </si>
-  <si>
-    <t>103060586647</t>
-  </si>
-  <si>
-    <t>Simpo Hitam</t>
+    <t>mug-kina-pink-150ml</t>
   </si>
 </sst>
 </file>
@@ -2895,17 +3147,17 @@
         <v>47</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2915,86 +3167,82 @@
     </row>
     <row customHeight="true" ht="15" r="8">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
       <c r="O8" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="9">
       <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
       <c r="O9" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="10">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>67</v>
@@ -3003,14 +3251,14 @@
         <v>68</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -3020,34 +3268,32 @@
     </row>
     <row customHeight="true" ht="15" r="11">
       <c r="A11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -3057,102 +3303,94 @@
     </row>
     <row customHeight="true" ht="15" r="12">
       <c r="A12" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>82</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E12" s="11"/>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
       <c r="O12" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="13">
       <c r="A13" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E13" s="11"/>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
       <c r="O13" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="14">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="5" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -3162,58 +3400,62 @@
     </row>
     <row customHeight="true" ht="15" r="15">
       <c r="A15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="11"/>
       <c r="F15" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+        <v>78</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
       <c r="O15" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="16">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="5" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
@@ -3224,65 +3466,67 @@
     </row>
     <row customHeight="true" ht="15" r="17">
       <c r="A17" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+        <v>105</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
       <c r="O17" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="18">
       <c r="A18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -3292,93 +3536,85 @@
     </row>
     <row customHeight="true" ht="15" r="19">
       <c r="A19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
       <c r="O19" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="20">
       <c r="A20" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E20" s="11"/>
       <c r="F20" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
       <c r="O20" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="21">
       <c r="A21" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="5" t="s">
@@ -3393,29 +3629,29 @@
     </row>
     <row customHeight="true" ht="15" r="22">
       <c r="A22" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="5" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>40</v>
@@ -3428,54 +3664,58 @@
     </row>
     <row customHeight="true" ht="15" r="23">
       <c r="A23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="11"/>
       <c r="F23" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
+      <c r="J23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
       <c r="O23" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="24">
       <c r="A24" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="5" t="s">
@@ -3490,27 +3730,27 @@
     </row>
     <row customHeight="true" ht="15" r="25">
       <c r="A25" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="5" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -3521,102 +3761,94 @@
     </row>
     <row customHeight="true" ht="15" r="26">
       <c r="A26" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E26" s="11"/>
       <c r="F26" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
       <c r="O26" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="27">
       <c r="A27" s="1" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E27" s="11"/>
       <c r="F27" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
       <c r="O27" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="28">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -3626,102 +3858,94 @@
     </row>
     <row customHeight="true" ht="15" r="29">
       <c r="A29" s="1" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E29" s="11"/>
       <c r="F29" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
       <c r="O29" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="30">
       <c r="A30" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>168</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="E30" s="11"/>
       <c r="F30" s="3" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
       <c r="O30" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="31">
       <c r="A31" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -3731,34 +3955,32 @@
     </row>
     <row customHeight="true" ht="15" r="32">
       <c r="A32" s="1" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="H32" s="3"/>
       <c r="I32" s="5" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -3768,32 +3990,32 @@
     </row>
     <row customHeight="true" ht="15" r="33">
       <c r="A33" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="5" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -3803,62 +4025,58 @@
     </row>
     <row customHeight="true" ht="15" r="34">
       <c r="A34" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>192</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="E34" s="11"/>
       <c r="F34" s="3" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
       <c r="O34" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="35">
       <c r="A35" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="5" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -3869,21 +4087,25 @@
     </row>
     <row customHeight="true" ht="15" r="36">
       <c r="A36" s="1" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="G36" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="5" t="s">
@@ -3900,28 +4122,32 @@
     </row>
     <row customHeight="true" ht="15" r="37">
       <c r="A37" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G37" s="4" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="5" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -3931,91 +4157,93 @@
     </row>
     <row customHeight="true" ht="15" r="38">
       <c r="A38" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G38" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
       <c r="O38" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="39">
       <c r="A39" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>211</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="E39" s="11"/>
       <c r="F39" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
       <c r="O39" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="40">
       <c r="A40" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="5" t="s">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -4026,27 +4254,27 @@
     </row>
     <row customHeight="true" ht="15" r="41">
       <c r="A41" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="3" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>213</v>
+        <v>62</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="5" t="s">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
@@ -4057,25 +4285,29 @@
     </row>
     <row customHeight="true" ht="15" r="42">
       <c r="A42" s="1" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="G42" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="5" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>40</v>
@@ -4088,85 +4320,93 @@
     </row>
     <row customHeight="true" ht="15" r="43">
       <c r="A43" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G43" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
       <c r="O43" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="44">
       <c r="A44" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="E44" s="11"/>
+      <c r="F44" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="G44" s="4" t="s">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
       <c r="O44" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="45">
       <c r="A45" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E45" s="11"/>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G45" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
@@ -4177,56 +4417,58 @@
     </row>
     <row customHeight="true" ht="15" r="46">
       <c r="A46" s="1" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+        <v>198</v>
+      </c>
+      <c r="E46" s="11"/>
+      <c r="F46" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G46" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
       <c r="O46" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="47">
       <c r="A47" s="1" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="E47" s="11"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G47" s="4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="5" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
@@ -4237,81 +4479,87 @@
     </row>
     <row customHeight="true" ht="15" r="48">
       <c r="A48" s="1" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+        <v>204</v>
+      </c>
+      <c r="E48" s="11"/>
+      <c r="F48" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="G48" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
       <c r="O48" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="49">
       <c r="A49" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="3"/>
+        <v>233</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G49" s="4" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
       <c r="O49" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="50">
       <c r="A50" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+        <v>238</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G50" s="4" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="5" t="s">
@@ -4334,115 +4582,127 @@
         <v>241</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="G51" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
+      <c r="J51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
       <c r="O51" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="52">
       <c r="A52" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="11"/>
+      <c r="F52" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
       <c r="G52" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
       <c r="O52" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="53">
       <c r="A53" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="3"/>
+        <v>250</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="G53" s="4" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
+        <v>253</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
       <c r="O53" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="54">
       <c r="A54" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="5" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
@@ -4452,56 +4712,58 @@
     </row>
     <row customHeight="true" ht="15" r="55">
       <c r="A55" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="G55" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
       <c r="O55" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="56">
       <c r="A56" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E56" s="11"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="G56" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="5" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
@@ -4512,79 +4774,89 @@
     </row>
     <row customHeight="true" ht="15" r="57">
       <c r="A57" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E57" s="11"/>
+      <c r="F57" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="G57" s="4" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
       <c r="O57" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="58">
       <c r="A58" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E58" s="11"/>
-      <c r="F58" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="G58" s="4" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
       <c r="O58" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="59">
       <c r="A59" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D59" s="2"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+      <c r="E59" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="G59" s="4" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="5" t="s">
@@ -4601,29 +4873,29 @@
     </row>
     <row customHeight="true" ht="15" r="60">
       <c r="A60" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>66</v>
+        <v>280</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>270</v>
+        <v>62</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="5" t="s">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>40</v>
@@ -4636,89 +4908,91 @@
     </row>
     <row customHeight="true" ht="15" r="61">
       <c r="A61" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+        <v>284</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E61" s="11"/>
+      <c r="F61" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="G61" s="4" t="s">
-        <v>274</v>
+        <v>62</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
       <c r="O61" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="62">
       <c r="A62" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>279</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="E62" s="11"/>
       <c r="F62" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
       <c r="O62" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="63">
       <c r="A63" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+        <v>293</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="G63" s="4" t="s">
-        <v>204</v>
+        <v>296</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="5" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>40</v>
@@ -4731,122 +5005,120 @@
     </row>
     <row customHeight="true" ht="15" r="64">
       <c r="A64" s="1" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="G64" s="4" t="s">
-        <v>207</v>
+        <v>302</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
       <c r="O64" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="65">
       <c r="A65" s="1" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>288</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E65" s="11"/>
       <c r="F65" s="3" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
       <c r="O65" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="66">
       <c r="A66" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>295</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E66" s="11"/>
       <c r="F66" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>297</v>
+        <v>49</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
       <c r="O66" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="67">
       <c r="A67" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>297</v>
+        <v>49</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="5" t="s">
@@ -4861,63 +5133,65 @@
     </row>
     <row customHeight="true" ht="15" r="68">
       <c r="A68" s="1" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E68" s="11"/>
+        <v>312</v>
+      </c>
+      <c r="D68" s="2"/>
+      <c r="E68" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="F68" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
+        <v>98</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
       <c r="O68" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="69">
       <c r="A69" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>307</v>
+        <v>46</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
@@ -4927,23 +5201,23 @@
     </row>
     <row customHeight="true" ht="15" r="70">
       <c r="A70" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="5" t="s">
@@ -4958,23 +5232,23 @@
     </row>
     <row customHeight="true" ht="15" r="71">
       <c r="A71" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="3" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="5" t="s">
@@ -4989,23 +5263,29 @@
     </row>
     <row customHeight="true" ht="15" r="72">
       <c r="A72" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
+        <v>328</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="G72" s="4" t="s">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="5" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>40</v>
@@ -5018,62 +5298,58 @@
     </row>
     <row customHeight="true" ht="15" r="73">
       <c r="A73" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="E73" s="11"/>
       <c r="F73" s="3" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
       <c r="O73" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="74">
       <c r="A74" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="3" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="5" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
@@ -5084,126 +5360,130 @@
     </row>
     <row customHeight="true" ht="15" r="75">
       <c r="A75" s="1" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E75" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="F75" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
+        <v>343</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
       <c r="O75" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="76">
       <c r="A76" s="1" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E76" s="11"/>
+        <v>347</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="F76" s="3" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
       <c r="O76" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="77">
       <c r="A77" s="1" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>334</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="E77" s="11"/>
       <c r="F77" s="3" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
       <c r="O77" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="78">
       <c r="A78" s="1" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>339</v>
+        <v>209</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="5" t="s">
-        <v>342</v>
+        <v>40</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>40</v>
@@ -5216,81 +5496,91 @@
     </row>
     <row customHeight="true" ht="15" r="79">
       <c r="A79" s="1" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E79" s="11"/>
+        <v>363</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="F79" s="3" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>48</v>
+        <v>366</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
       <c r="O79" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="80">
       <c r="A80" s="1" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E80" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="F80" s="3" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
       <c r="O80" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="81">
       <c r="A81" s="1" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="D81" s="2"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
+      <c r="E81" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="G81" s="4" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="5" t="s">
@@ -5307,29 +5597,29 @@
     </row>
     <row customHeight="true" ht="15" r="82">
       <c r="A82" s="1" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="5" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>40</v>
@@ -5342,93 +5632,93 @@
     </row>
     <row customHeight="true" ht="15" r="83">
       <c r="A83" s="1" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>363</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="E83" s="11"/>
       <c r="F83" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>158</v>
+        <v>350</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
       <c r="O83" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="84">
       <c r="A84" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E84" s="11"/>
+        <v>352</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="F84" s="3" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>158</v>
+        <v>354</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
       <c r="O84" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="85">
       <c r="A85" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>66</v>
+        <v>347</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="3" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="5" t="s">
-        <v>290</v>
+        <v>164</v>
       </c>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
@@ -5439,63 +5729,67 @@
     </row>
     <row customHeight="true" ht="15" r="86">
       <c r="A86" s="1" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E86" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="F86" s="3" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
+        <v>105</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
       <c r="O86" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="87">
       <c r="A87" s="1" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="5" t="s">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
@@ -5505,118 +5799,126 @@
     </row>
     <row customHeight="true" ht="15" r="88">
       <c r="A88" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>383</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="E88" s="11"/>
       <c r="F88" s="3" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>158</v>
+        <v>350</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J88" s="11"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
+      <c r="N88" s="11"/>
       <c r="O88" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="89">
       <c r="A89" s="1" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E89" s="11"/>
+        <v>352</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>408</v>
+      </c>
       <c r="F89" s="3" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>158</v>
+        <v>354</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
       <c r="O89" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="90">
       <c r="A90" s="1" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
+        <v>410</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E90" s="11"/>
+      <c r="F90" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="G90" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
+      <c r="N90" s="11"/>
       <c r="O90" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="91">
       <c r="A91" s="1" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
+        <v>414</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>416</v>
+      </c>
       <c r="G91" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="5" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>40</v>
@@ -5629,93 +5931,93 @@
     </row>
     <row customHeight="true" ht="15" r="92">
       <c r="A92" s="1" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>397</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="E92" s="11"/>
       <c r="F92" s="3" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>158</v>
+        <v>350</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
+      <c r="N92" s="11"/>
       <c r="O92" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="93">
       <c r="A93" s="1" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E93" s="11"/>
+        <v>347</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="F93" s="3" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>158</v>
+        <v>383</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
       <c r="O93" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="94">
       <c r="A94" s="1" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>402</v>
+        <v>352</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="3" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>199</v>
+        <v>350</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="5" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="J94" s="11"/>
       <c r="K94" s="11"/>
@@ -5726,54 +6028,58 @@
     </row>
     <row customHeight="true" ht="15" r="95">
       <c r="A95" s="1" t="s">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E95" s="11"/>
+        <v>347</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>429</v>
+      </c>
       <c r="F95" s="3" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>158</v>
+        <v>350</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
-      <c r="M95" s="11"/>
-      <c r="N95" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
       <c r="O95" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="96">
       <c r="A96" s="1" t="s">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="3" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>158</v>
+        <v>354</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="5" t="s">
@@ -5788,98 +6094,98 @@
     </row>
     <row customHeight="true" ht="15" r="97">
       <c r="A97" s="1" t="s">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>394</v>
+        <v>434</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E97" s="11"/>
+        <v>347</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>436</v>
+      </c>
       <c r="F97" s="3" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>145</v>
+        <v>350</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J97" s="11"/>
-      <c r="K97" s="11"/>
-      <c r="L97" s="11"/>
-      <c r="M97" s="11"/>
-      <c r="N97" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
       <c r="O97" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="98">
       <c r="A98" s="1" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>414</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="E98" s="11"/>
       <c r="F98" s="3" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
+      <c r="N98" s="11"/>
       <c r="O98" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="99">
       <c r="A99" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>219</v>
+        <v>46</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="5" t="s">
-        <v>40</v>
+        <v>446</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
@@ -5889,23 +6195,23 @@
     </row>
     <row customHeight="true" ht="15" r="100">
       <c r="A100" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="3" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="5" t="s">
@@ -5920,27 +6226,27 @@
     </row>
     <row customHeight="true" ht="15" r="101">
       <c r="A101" s="1" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>366</v>
+        <v>59</v>
       </c>
       <c r="E101" s="11"/>
       <c r="F101" s="3" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="5" t="s">
-        <v>229</v>
+        <v>451</v>
       </c>
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
@@ -5951,91 +6257,91 @@
     </row>
     <row customHeight="true" ht="15" r="102">
       <c r="A102" s="1" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E102" s="11"/>
+        <v>352</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>455</v>
+      </c>
       <c r="F102" s="3" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>426</v>
+        <v>354</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J102" s="11"/>
-      <c r="K102" s="11"/>
-      <c r="L102" s="11"/>
-      <c r="M102" s="11"/>
-      <c r="N102" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
       <c r="O102" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="103">
       <c r="A103" s="1" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>430</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="E103" s="11"/>
       <c r="F103" s="3" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="J103" s="11"/>
+      <c r="K103" s="11"/>
+      <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
+      <c r="N103" s="11"/>
       <c r="O103" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="104">
       <c r="A104" s="1" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>435</v>
+        <v>281</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="5" t="s">
@@ -6052,28 +6358,32 @@
     </row>
     <row customHeight="true" ht="15" r="105">
       <c r="A105" s="1" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
+        <v>92</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>467</v>
+      </c>
       <c r="G105" s="4" t="s">
-        <v>441</v>
+        <v>49</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
@@ -6083,25 +6393,27 @@
     </row>
     <row customHeight="true" ht="15" r="106">
       <c r="A106" s="1" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>443</v>
+        <v>53</v>
       </c>
       <c r="E106" s="11"/>
-      <c r="F106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>469</v>
+      </c>
       <c r="G106" s="4" t="s">
-        <v>441</v>
+        <v>49</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -6112,61 +6424,69 @@
     </row>
     <row customHeight="true" ht="15" r="107">
       <c r="A107" s="1" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E107" s="11"/>
-      <c r="F107" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>474</v>
+      </c>
       <c r="G107" s="4" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J107" s="11"/>
-      <c r="K107" s="11"/>
-      <c r="L107" s="11"/>
-      <c r="M107" s="11"/>
-      <c r="N107" s="11"/>
+        <v>476</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
       <c r="O107" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="108">
       <c r="A108" s="1" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="H108" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="I108" s="5" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
@@ -6176,32 +6496,32 @@
     </row>
     <row customHeight="true" ht="15" r="109">
       <c r="A109" s="1" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>48</v>
+        <v>489</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
@@ -6211,32 +6531,32 @@
     </row>
     <row customHeight="true" ht="15" r="110">
       <c r="A110" s="1" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>460</v>
+        <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>463</v>
+        <v>104</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="5" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
@@ -6246,92 +6566,104 @@
     </row>
     <row customHeight="true" ht="15" r="111">
       <c r="A111" s="1" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>458</v>
+        <v>496</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E111" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="F111" s="3" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J111" s="11"/>
-      <c r="K111" s="11"/>
-      <c r="L111" s="11"/>
-      <c r="M111" s="11"/>
-      <c r="N111" s="11"/>
+      <c r="J111" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
       <c r="O111" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="112">
       <c r="A112" s="1" t="s">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>458</v>
+        <v>502</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E112" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="F112" s="3" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J112" s="11"/>
-      <c r="K112" s="11"/>
-      <c r="L112" s="11"/>
-      <c r="M112" s="11"/>
-      <c r="N112" s="11"/>
+      <c r="J112" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
       <c r="O112" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="113">
       <c r="A113" s="1" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E113" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="F113" s="3" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="H113" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="I113" s="5" t="s">
         <v>40</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
@@ -6341,85 +6673,93 @@
     </row>
     <row customHeight="true" ht="15" r="114">
       <c r="A114" s="1" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E114" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="F114" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J114" s="11"/>
-      <c r="K114" s="11"/>
-      <c r="L114" s="11"/>
-      <c r="M114" s="11"/>
-      <c r="N114" s="11"/>
+        <v>516</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
       <c r="O114" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="115">
       <c r="A115" s="1" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E115" s="11"/>
+        <v>520</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>521</v>
+      </c>
       <c r="F115" s="3" t="s">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J115" s="11"/>
-      <c r="K115" s="11"/>
-      <c r="L115" s="11"/>
-      <c r="M115" s="11"/>
-      <c r="N115" s="11"/>
+        <v>78</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
       <c r="O115" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="116">
       <c r="A116" s="1" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>478</v>
+        <v>523</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>215</v>
+        <v>524</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="3" t="s">
-        <v>479</v>
+        <v>525</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="5" t="s">
@@ -6434,23 +6774,23 @@
     </row>
     <row customHeight="true" ht="15" r="117">
       <c r="A117" s="1" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>480</v>
+        <v>526</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>481</v>
+        <v>527</v>
       </c>
       <c r="E117" s="11"/>
       <c r="F117" s="3" t="s">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="5" t="s">
@@ -6465,65 +6805,63 @@
     </row>
     <row customHeight="true" ht="15" r="118">
       <c r="A118" s="1" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>485</v>
+        <v>529</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>486</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="E118" s="11"/>
       <c r="F118" s="3" t="s">
-        <v>486</v>
+        <v>531</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>487</v>
+        <v>74</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="J118" s="11"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11"/>
       <c r="O118" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="119">
       <c r="A119" s="1" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E119" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>535</v>
+      </c>
       <c r="F119" s="3" t="s">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>493</v>
+        <v>537</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K119" s="3"/>
       <c r="L119" s="3"/>
@@ -6533,54 +6871,58 @@
     </row>
     <row customHeight="true" ht="15" r="120">
       <c r="A120" s="1" t="s">
-        <v>489</v>
+        <v>538</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>494</v>
+        <v>540</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E120" s="11"/>
+        <v>92</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>541</v>
+      </c>
       <c r="F120" s="3" t="s">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>493</v>
+        <v>49</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J120" s="11"/>
-      <c r="K120" s="11"/>
-      <c r="L120" s="11"/>
-      <c r="M120" s="11"/>
-      <c r="N120" s="11"/>
+      <c r="J120" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
       <c r="O120" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="121">
       <c r="A121" s="1" t="s">
-        <v>489</v>
+        <v>538</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>496</v>
+        <v>543</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>215</v>
+        <v>53</v>
       </c>
       <c r="E121" s="11"/>
       <c r="F121" s="3" t="s">
-        <v>497</v>
+        <v>544</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>493</v>
+        <v>49</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="5" t="s">
@@ -6595,23 +6937,23 @@
     </row>
     <row customHeight="true" ht="15" r="122">
       <c r="A122" s="1" t="s">
-        <v>489</v>
+        <v>538</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>498</v>
+        <v>545</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>122</v>
+        <v>308</v>
       </c>
       <c r="E122" s="11"/>
       <c r="F122" s="3" t="s">
-        <v>499</v>
+        <v>546</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>493</v>
+        <v>49</v>
       </c>
       <c r="H122" s="3"/>
       <c r="I122" s="5" t="s">
@@ -6624,6 +6966,284 @@
       <c r="N122" s="11"/>
       <c r="O122" s="6"/>
     </row>
+    <row customHeight="true" ht="15" r="123">
+      <c r="A123" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E123" s="11"/>
+      <c r="F123" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J123" s="11"/>
+      <c r="K123" s="11"/>
+      <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
+      <c r="N123" s="11"/>
+      <c r="O123" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="124">
+      <c r="A124" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H124" s="3"/>
+      <c r="I124" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+      <c r="O124" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="125">
+      <c r="A125" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H125" s="3"/>
+      <c r="I125" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="126">
+      <c r="A126" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="127">
+      <c r="A127" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="H127" s="3"/>
+      <c r="I127" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="128">
+      <c r="A128" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="129">
+      <c r="A129" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E129" s="11"/>
+      <c r="F129" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+      <c r="N129" s="11"/>
+      <c r="O129" s="6"/>
+    </row>
+    <row customHeight="true" ht="15" r="130">
+      <c r="A130" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H130" s="3"/>
+      <c r="I130" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="6"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="true" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
 </worksheet>
